--- a/data/trans_dic/P19C09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,48</t>
+          <t>0,26; 2,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,98</t>
+          <t>0,86; 3,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,8</t>
+          <t>1,84; 5,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,77</t>
+          <t>0,48; 2,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,27</t>
+          <t>1,64; 5,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,02</t>
+          <t>0,85; 4,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,02</t>
+          <t>0,5; 2,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,03</t>
+          <t>1,6; 3,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,16</t>
+          <t>1,7; 4,28</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,77</t>
+          <t>0,98; 3,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,41</t>
+          <t>0,97; 3,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,03</t>
+          <t>1,78; 5,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,02</t>
+          <t>1,27; 4,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,36</t>
+          <t>2,1; 5,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,25</t>
+          <t>1,97; 5,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,27</t>
+          <t>1,42; 3,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,81</t>
+          <t>1,79; 3,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,38</t>
+          <t>2,21; 4,43</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,26</t>
+          <t>1,36; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,93</t>
+          <t>0,55; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,49</t>
+          <t>2,06; 5,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,35</t>
+          <t>0,96; 3,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,39</t>
+          <t>1,36; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,8</t>
+          <t>1,12; 3,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,07</t>
+          <t>1,34; 3,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,05</t>
+          <t>1,19; 3,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,82</t>
+          <t>1,85; 3,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,87</t>
+          <t>0,49; 3,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,38</t>
+          <t>0,4; 2,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,71</t>
+          <t>1,03; 3,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,45</t>
+          <t>1,86; 5,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,45</t>
+          <t>0,85; 3,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,25</t>
+          <t>1,19; 4,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,86</t>
+          <t>1,57; 3,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,43</t>
+          <t>0,83; 2,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,57</t>
+          <t>1,54; 3,48</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,32</t>
+          <t>1,71; 6,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,27</t>
+          <t>0,59; 3,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,69</t>
+          <t>0,7; 3,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,67</t>
+          <t>3,68; 8,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,37</t>
+          <t>1,06; 4,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,22</t>
+          <t>2,2; 6,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,71</t>
+          <t>3,29; 6,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,37</t>
+          <t>1,22; 3,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,27</t>
+          <t>1,8; 4,29</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,7</t>
+          <t>2,27; 7,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,18</t>
+          <t>1,87; 8,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,6</t>
+          <t>0,81; 4,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,14</t>
+          <t>3,48; 9,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,69</t>
+          <t>1,0; 4,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,23</t>
+          <t>0,74; 4,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,61</t>
+          <t>3,37; 7,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,09</t>
+          <t>1,81; 5,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,64</t>
+          <t>1,14; 3,84</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 15,49</t>
+          <t>5,07; 15,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 10,67</t>
+          <t>2,86; 10,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,73</t>
+          <t>2,22; 8,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,13</t>
+          <t>2,68; 7,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,5</t>
+          <t>0,81; 6,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 9,98</t>
+          <t>4,01; 9,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,0</t>
+          <t>1,75; 5,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,45</t>
+          <t>2,09; 6,48</t>
         </is>
       </c>
     </row>
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,22; 2,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,64</t>
+          <t>2,31; 3,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,9</t>
+          <t>2,51; 3,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,48</t>
+          <t>2,17; 3,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,34</t>
+          <t>2,09; 3,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,43</t>
+          <t>2,45; 3,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,76</t>
+          <t>1,88; 2,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,2</t>
+          <t>2,35; 3,24</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>928; 8909</t>
+          <t>944; 9302</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3687; 14579</t>
+          <t>3152; 14001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6436; 20452</t>
+          <t>6478; 20372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1860; 10411</t>
+          <t>1821; 10441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5581; 19057</t>
+          <t>5942; 20823</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3741; 14131</t>
+          <t>3002; 14398</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3854; 14844</t>
+          <t>3698; 15875</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12630; 29298</t>
+          <t>11668; 28555</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12083; 29286</t>
+          <t>12008; 30196</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6255; 21697</t>
+          <t>5663; 21419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5618; 20081</t>
+          <t>5690; 19675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8575; 24826</t>
+          <t>8788; 24786</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7044; 22030</t>
+          <t>6955; 22179</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11896; 29004</t>
+          <t>11377; 29442</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9307; 26065</t>
+          <t>9794; 25717</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15561; 36774</t>
+          <t>15938; 36687</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19795; 43109</t>
+          <t>20256; 42748</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20902; 43334</t>
+          <t>21904; 43844</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6685; 21358</t>
+          <t>6826; 21309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2946; 16726</t>
+          <t>3131; 16915</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11745; 30641</t>
+          <t>11510; 30269</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6017; 20142</t>
+          <t>5764; 19128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8610; 28251</t>
+          <t>8743; 27875</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6890; 21754</t>
+          <t>6398; 20763</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15041; 33873</t>
+          <t>14825; 34964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14463; 37068</t>
+          <t>14427; 36847</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21523; 43163</t>
+          <t>20895; 43051</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1943; 15649</t>
+          <t>1989; 15041</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2892; 12403</t>
+          <t>2086; 12183</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5235; 19027</t>
+          <t>5271; 19935</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8570; 23923</t>
+          <t>8171; 23904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4436; 18855</t>
+          <t>4625; 19357</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7312; 23170</t>
+          <t>6505; 21800</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12735; 32563</t>
+          <t>13242; 31959</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8461; 25899</t>
+          <t>8862; 26448</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15239; 37705</t>
+          <t>16231; 36825</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4786; 17162</t>
+          <t>4647; 17342</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2002; 11411</t>
+          <t>2051; 12291</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2286; 13681</t>
+          <t>2592; 13485</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10683; 27522</t>
+          <t>11695; 28079</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3998; 16706</t>
+          <t>4053; 17480</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7907; 24610</t>
+          <t>8697; 24953</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18917; 39515</t>
+          <t>19361; 39378</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8871; 24663</t>
+          <t>8943; 23782</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12874; 32753</t>
+          <t>13808; 32878</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4604; 16275</t>
+          <t>4788; 16515</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4229; 18766</t>
+          <t>4899; 21586</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1892; 10588</t>
+          <t>1854; 10467</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8527; 22559</t>
+          <t>8585; 22406</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2944; 13921</t>
+          <t>2967; 13628</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2018; 11721</t>
+          <t>2038; 12684</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16010; 34868</t>
+          <t>15425; 32781</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9410; 28382</t>
+          <t>10102; 28226</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5719; 18459</t>
+          <t>5804; 19456</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6407; 19632</t>
+          <t>6432; 19914</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4734</t>
+          <t>0; 5221</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4170; 15696</t>
+          <t>4204; 15014</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4661; 18172</t>
+          <t>4613; 18019</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7384; 24241</t>
+          <t>7977; 23744</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1996; 14817</t>
+          <t>1837; 14920</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13861; 33444</t>
+          <t>13443; 32073</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8343; 23851</t>
+          <t>8367; 24187</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7826; 24167</t>
+          <t>7832; 24294</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49747; 80395</t>
+          <t>49811; 80461</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35840; 65963</t>
+          <t>34584; 63186</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>61151; 96900</t>
+          <t>61511; 96961</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>69534; 106829</t>
+          <t>68707; 105070</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>68765; 106697</t>
+          <t>66714; 105433</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59388; 95811</t>
+          <t>59852; 96283</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>126092; 178096</t>
+          <t>127168; 175380</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>114248; 163248</t>
+          <t>111290; 159439</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>128980; 177268</t>
+          <t>130042; 179356</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Edad-trans_dic.xlsx
@@ -678,42 +678,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,59</t>
+          <t>0,25; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,82</t>
+          <t>1,02; 3,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,77</t>
+          <t>1,78; 6,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,77</t>
+          <t>0,49; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,76</t>
+          <t>1,66; 5,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,09</t>
+          <t>1,07; 4,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,16</t>
+          <t>0,51; 2,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,93</t>
+          <t>1,62; 3,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,72</t>
+          <t>0,97; 3,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,34</t>
+          <t>0,96; 3,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,03</t>
+          <t>1,76; 4,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,05</t>
+          <t>1,23; 3,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,44</t>
+          <t>2,12; 5,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,18</t>
+          <t>1,91; 5,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,27</t>
+          <t>1,35; 3,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,78</t>
+          <t>1,71; 3,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,43</t>
+          <t>2,21; 4,54</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,25</t>
+          <t>1,33; 4,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,96</t>
+          <t>0,51; 2,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,43</t>
+          <t>1,94; 5,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,18</t>
+          <t>0,87; 3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,33</t>
+          <t>1,43; 4,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,62</t>
+          <t>1,13; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,17</t>
+          <t>1,4; 3,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,03</t>
+          <t>1,24; 3,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,81</t>
+          <t>1,9; 3,85</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,72</t>
+          <t>0,61; 3,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,34</t>
+          <t>0,4; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,89</t>
+          <t>1,02; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,44</t>
+          <t>1,94; 5,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,54</t>
+          <t>0,82; 3,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,0</t>
+          <t>1,34; 4,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,79</t>
+          <t>1,56; 3,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,48</t>
+          <t>0,83; 2,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,48</t>
+          <t>1,46; 3,31</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,39</t>
+          <t>1,72; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,52</t>
+          <t>0,58; 3,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,63</t>
+          <t>0,86; 3,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 8,85</t>
+          <t>3,63; 8,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,57</t>
+          <t>1,0; 4,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,3</t>
+          <t>2,18; 6,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,69</t>
+          <t>3,23; 6,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,25</t>
+          <t>1,2; 3,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,29</t>
+          <t>1,71; 4,26</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 7,82</t>
+          <t>2,16; 7,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,26</t>
+          <t>1,91; 7,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,55</t>
+          <t>0,81; 4,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,07</t>
+          <t>3,39; 9,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,59</t>
+          <t>0,99; 4,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,58</t>
+          <t>0,76; 4,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,15</t>
+          <t>3,53; 7,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,06</t>
+          <t>1,79; 5,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,84</t>
+          <t>1,1; 3,51</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,07; 15,71</t>
+          <t>5,02; 15,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 10,21</t>
+          <t>2,83; 10,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,65</t>
+          <t>2,21; 8,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,97</t>
+          <t>2,78; 8,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,55</t>
+          <t>0,87; 6,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 9,57</t>
+          <t>4,12; 9,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,07</t>
+          <t>1,74; 5,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,48</t>
+          <t>2,06; 6,55</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,28</t>
+          <t>2,03; 3,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,23</t>
+          <t>1,3; 2,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,64</t>
+          <t>2,26; 3,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,84</t>
+          <t>2,54; 3,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,43</t>
+          <t>2,25; 3,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,36</t>
+          <t>2,13; 3,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,38</t>
+          <t>2,44; 3,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,7</t>
+          <t>1,88; 2,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,24</t>
+          <t>2,36; 3,27</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>944; 9302</t>
+          <t>914; 8284</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3152; 14001</t>
+          <t>3753; 14411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6478; 20372</t>
+          <t>6288; 21532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1821; 10441</t>
+          <t>1829; 11301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5942; 20823</t>
+          <t>6005; 19369</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3002; 14398</t>
+          <t>3750; 15218</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3698; 15875</t>
+          <t>3737; 15326</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11668; 28555</t>
+          <t>11810; 28146</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12008; 30196</t>
+          <t>11988; 30191</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5663; 21419</t>
+          <t>5596; 21298</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5690; 19675</t>
+          <t>5662; 19815</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8788; 24786</t>
+          <t>8701; 24389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6955; 22179</t>
+          <t>6758; 21098</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11377; 29442</t>
+          <t>11507; 29748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9794; 25717</t>
+          <t>9477; 25945</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15938; 36687</t>
+          <t>15153; 37122</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20256; 42748</t>
+          <t>19295; 43427</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21904; 43844</t>
+          <t>21911; 44898</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6826; 21309</t>
+          <t>6668; 21887</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3131; 16915</t>
+          <t>2891; 14967</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11510; 30269</t>
+          <t>10839; 30361</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5764; 19128</t>
+          <t>5228; 19869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8743; 27875</t>
+          <t>9174; 29025</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6398; 20763</t>
+          <t>6492; 21063</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14825; 34964</t>
+          <t>15403; 34183</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14427; 36847</t>
+          <t>15042; 38556</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20895; 43051</t>
+          <t>21469; 43503</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1989; 15041</t>
+          <t>2485; 15744</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2086; 12183</t>
+          <t>2099; 12414</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5271; 19935</t>
+          <t>5223; 18995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8171; 23904</t>
+          <t>8537; 24772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4625; 19357</t>
+          <t>4493; 20329</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6505; 21800</t>
+          <t>7326; 23259</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13242; 31959</t>
+          <t>13176; 32076</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8862; 26448</t>
+          <t>8846; 25679</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16231; 36825</t>
+          <t>15436; 34985</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4647; 17342</t>
+          <t>4676; 16225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2051; 12291</t>
+          <t>2035; 12141</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2592; 13485</t>
+          <t>3208; 14131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11695; 28079</t>
+          <t>11526; 27896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4053; 17480</t>
+          <t>3814; 17071</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8697; 24953</t>
+          <t>8641; 24810</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19361; 39378</t>
+          <t>19011; 38969</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8943; 23782</t>
+          <t>8812; 25455</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13808; 32878</t>
+          <t>13087; 32670</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4788; 16515</t>
+          <t>4556; 16143</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4899; 21586</t>
+          <t>4986; 20217</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1854; 10467</t>
+          <t>1870; 11155</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8585; 22406</t>
+          <t>8381; 22939</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2967; 13628</t>
+          <t>2951; 12999</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2038; 12684</t>
+          <t>2109; 12541</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15425; 32781</t>
+          <t>16174; 33725</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10102; 28226</t>
+          <t>9984; 28030</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5804; 19456</t>
+          <t>5572; 17807</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6432; 19914</t>
+          <t>6362; 20115</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5221</t>
+          <t>0; 6358</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4204; 15014</t>
+          <t>4169; 15398</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4613; 18019</t>
+          <t>4597; 18029</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7977; 23744</t>
+          <t>8292; 23846</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1837; 14920</t>
+          <t>1991; 14902</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13443; 32073</t>
+          <t>13792; 32585</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8367; 24187</t>
+          <t>8282; 24434</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7832; 24294</t>
+          <t>7710; 24571</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49811; 80461</t>
+          <t>49727; 81908</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34584; 63186</t>
+          <t>36997; 66974</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>61511; 96961</t>
+          <t>60098; 94125</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>68707; 105070</t>
+          <t>69568; 105202</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>66714; 105433</t>
+          <t>69078; 106971</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59852; 96283</t>
+          <t>61045; 97964</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>127168; 175380</t>
+          <t>126470; 175335</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>111290; 159439</t>
+          <t>111187; 160618</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>130042; 179356</t>
+          <t>130383; 180676</t>
         </is>
       </c>
     </row>
